--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27447,16 +27447,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O141" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.7786361057381954</v>
+        <v>0.7896545411967548</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27609,10 +27609,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O142" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27843,16 +27843,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="O143" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>4.854614659099075</v>
+        <v>4.856552629022867</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29998,7 +29998,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30800,7 +30800,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31199,16 +31199,16 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O160" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.1322212255027125</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -31361,10 +31361,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O161" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31595,16 +31595,16 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="O162" t="n">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>0.6724755635558399</v>
+        <v>0.7461184206599377</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>327137</v>
+        <v>327189</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27447,16 +27447,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O141" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.7896545411967548</v>
+        <v>0.7933273530162747</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27609,10 +27609,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O142" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27843,16 +27843,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="O143" t="n">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>4.856552629022867</v>
+        <v>4.860428568870451</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29196,7 +29196,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29998,7 +29998,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30800,7 +30800,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31199,16 +31199,16 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="O160" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.1689493436979103</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -31361,10 +31361,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="O161" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31595,16 +31595,16 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="O162" t="n">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>0.7461184206599377</v>
+        <v>1.069759397933209</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>327189</v>
+        <v>327369</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -27447,16 +27447,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O141" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.7933273530162747</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27609,10 +27609,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O142" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -27843,16 +27843,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="O143" t="n">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>4.860428568870451</v>
+        <v>4.858490598946659</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -31199,16 +31199,16 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O160" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1689493436979103</v>
+        <v>0.1432396609612718</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -31361,10 +31361,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O161" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -31595,16 +31595,16 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="O162" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>1.069759397933209</v>
+        <v>1.100766916713882</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -31821,6 +31821,660 @@
       <c r="BC163" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>594</v>
+      </c>
+      <c r="O164" t="n">
+        <v>594</v>
+      </c>
+      <c r="P164" t="n">
+        <v>594</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>19</v>
+      </c>
+      <c r="O165" t="n">
+        <v>19</v>
+      </c>
+      <c r="P165" t="n">
+        <v>19</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>594</v>
+      </c>
+      <c r="O166" t="n">
+        <v>594</v>
+      </c>
+      <c r="P166" t="n">
+        <v>594</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31857,7 +32511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -31940,7 +32594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -31950,7 +32604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -31970,7 +32624,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -32002,7 +32656,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>327369</v>
+        <v>327972</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>91</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1468,9 +1465,6 @@
       <c r="O6" t="n">
         <v>166</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>2.249748665126538</v>
       </c>
@@ -1616,9 +1610,6 @@
       <c r="O7" t="n">
         <v>2539</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>4.920505636508004</v>
       </c>
@@ -1915,9 +1906,6 @@
       <c r="P9" t="n">
         <v>493</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.4026865449299228</v>
       </c>
@@ -2172,7 +2160,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2414,7 +2402,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2717,9 +2705,6 @@
       <c r="P13" t="n">
         <v>1308</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.068385397096022</v>
       </c>
@@ -2974,7 +2959,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3216,7 +3201,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3519,9 +3504,6 @@
       <c r="P17" t="n">
         <v>715</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.5840180114095228</v>
       </c>
@@ -3776,7 +3758,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4018,7 +4000,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4321,9 +4303,6 @@
       <c r="P21" t="n">
         <v>960</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.7841360712631356</v>
       </c>
@@ -4578,7 +4557,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -4820,7 +4799,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5282,9 +5261,6 @@
       <c r="O26" t="n">
         <v>66</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5823,9 +5799,6 @@
       <c r="O29" t="n">
         <v>148</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>2.00580001469113</v>
       </c>
@@ -5974,9 +5947,6 @@
       <c r="P30" t="n">
         <v>712</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5815675861868256</v>
       </c>
@@ -6231,7 +6201,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6473,7 +6443,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6625,9 +6595,6 @@
       <c r="O33" t="n">
         <v>1558</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>3.019357141268007</v>
       </c>
@@ -6924,9 +6891,6 @@
       <c r="P35" t="n">
         <v>770</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.6289424738256401</v>
       </c>
@@ -7181,7 +7145,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7423,7 +7387,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7726,9 +7690,6 @@
       <c r="P39" t="n">
         <v>683</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.5578801423674183</v>
       </c>
@@ -7983,7 +7944,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8225,7 +8186,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8528,9 +8489,6 @@
       <c r="P43" t="n">
         <v>749</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.6117894972667589</v>
       </c>
@@ -8785,7 +8743,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9027,7 +8985,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9489,9 +9447,6 @@
       <c r="O48" t="n">
         <v>69</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10030,9 +9985,6 @@
       <c r="O51" t="n">
         <v>156</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>2.114221637106867</v>
       </c>
@@ -10181,9 +10133,6 @@
       <c r="P52" t="n">
         <v>663</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.541543974216103</v>
       </c>
@@ -10438,7 +10387,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10680,7 +10629,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10832,9 +10781,6 @@
       <c r="O55" t="n">
         <v>2137</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>4.141441727143602</v>
       </c>
@@ -11131,9 +11077,6 @@
       <c r="P57" t="n">
         <v>757</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.6183239645272851</v>
       </c>
@@ -11388,7 +11331,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11630,7 +11573,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11933,9 +11876,6 @@
       <c r="P61" t="n">
         <v>701</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.5725826937036022</v>
       </c>
@@ -12190,7 +12130,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12432,7 +12372,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12735,9 +12675,6 @@
       <c r="P65" t="n">
         <v>781</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.6379273663088634</v>
       </c>
@@ -12992,7 +12929,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13234,7 +13171,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13537,9 +13474,6 @@
       <c r="P69" t="n">
         <v>724</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.5913692870776148</v>
       </c>
@@ -13794,7 +13728,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14036,7 +13970,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14188,9 +14122,6 @@
       <c r="O72" t="n">
         <v>189</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.6941614338892403</v>
       </c>
@@ -14350,9 +14281,6 @@
       <c r="O73" t="n">
         <v>113</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14891,9 +14819,6 @@
       <c r="O76" t="n">
         <v>108</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.463691902612446</v>
       </c>
@@ -15039,9 +14964,6 @@
       <c r="O77" t="n">
         <v>3870</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>7.499943605075218</v>
       </c>
@@ -15338,9 +15260,6 @@
       <c r="P79" t="n">
         <v>738</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.6028046047835355</v>
       </c>
@@ -15595,7 +15514,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15837,7 +15756,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16140,9 +16059,6 @@
       <c r="P83" t="n">
         <v>736</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.601170987968404</v>
       </c>
@@ -16397,7 +16313,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16639,7 +16555,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16942,9 +16858,6 @@
       <c r="P87" t="n">
         <v>726</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.5930029038927463</v>
       </c>
@@ -17199,7 +17112,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -17441,7 +17354,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17744,9 +17657,6 @@
       <c r="P91" t="n">
         <v>861</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.7032720389141247</v>
       </c>
@@ -18001,7 +17911,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -18243,7 +18153,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18395,9 +18305,6 @@
       <c r="O94" t="n">
         <v>217</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.7970001648357945</v>
       </c>
@@ -18557,9 +18464,6 @@
       <c r="O95" t="n">
         <v>80</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19098,9 +19002,6 @@
       <c r="O98" t="n">
         <v>137</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.856720283869492</v>
       </c>
@@ -19246,9 +19147,6 @@
       <c r="O99" t="n">
         <v>4684</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>9.077451123041943</v>
       </c>
@@ -19545,9 +19443,6 @@
       <c r="P101" t="n">
         <v>849</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.6934703380233356</v>
       </c>
@@ -19802,7 +19697,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -20044,7 +19939,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20347,9 +20242,6 @@
       <c r="P105" t="n">
         <v>874</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.7138905482124798</v>
       </c>
@@ -20604,7 +20496,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -20846,7 +20738,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21149,9 +21041,6 @@
       <c r="P109" t="n">
         <v>1095</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.894405206284514</v>
       </c>
@@ -21406,7 +21295,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -21648,7 +21537,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -21951,9 +21840,6 @@
       <c r="P113" t="n">
         <v>870</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.7106233145822167</v>
       </c>
@@ -22208,7 +22094,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -22450,7 +22336,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -22602,9 +22488,6 @@
       <c r="O116" t="n">
         <v>28</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.00802210677175428</v>
       </c>
@@ -22753,9 +22636,6 @@
       <c r="P117" t="n">
         <v>999</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.8159915991582005</v>
       </c>
@@ -23010,7 +22890,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23252,7 +23132,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -23404,9 +23284,6 @@
       <c r="O120" t="n">
         <v>156</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.5729586438450872</v>
       </c>
@@ -23948,9 +23825,6 @@
       <c r="O123" t="n">
         <v>147</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.992247311889163</v>
       </c>
@@ -24096,9 +23970,6 @@
       <c r="O124" t="n">
         <v>3557</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>6.893359018928308</v>
       </c>
@@ -24244,9 +24115,6 @@
       <c r="O125" t="n">
         <v>34</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -24395,9 +24263,6 @@
       <c r="P126" t="n">
         <v>823</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.6722333194266257</v>
       </c>
@@ -24652,7 +24517,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -24894,7 +24759,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25046,9 +24911,6 @@
       <c r="O129" t="n">
         <v>42</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -25197,9 +25059,6 @@
       <c r="P130" t="n">
         <v>987</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.8061898982674113</v>
       </c>
@@ -25454,7 +25313,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -25696,7 +25555,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -25848,9 +25707,6 @@
       <c r="O133" t="n">
         <v>39</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -25999,9 +25855,6 @@
       <c r="P134" t="n">
         <v>781</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.6379273663088634</v>
       </c>
@@ -26256,7 +26109,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26498,7 +26351,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -26650,9 +26503,6 @@
       <c r="O137" t="n">
         <v>31</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.008881618211585096</v>
       </c>
@@ -26801,9 +26651,6 @@
       <c r="P138" t="n">
         <v>949</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.7751511787799122</v>
       </c>
@@ -27058,7 +26905,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -27300,7 +27147,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -27452,9 +27299,6 @@
       <c r="O141" t="n">
         <v>217</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.7970001648357945</v>
       </c>
@@ -27843,16 +27687,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="O143" t="n">
-        <v>2507</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
+        <v>2508</v>
       </c>
       <c r="R143" t="n">
-        <v>4.858490598946659</v>
+        <v>4.860428568870451</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27996,9 +27837,6 @@
       <c r="O144" t="n">
         <v>26</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.007449099145200401</v>
       </c>
@@ -28147,9 +27985,6 @@
       <c r="P145" t="n">
         <v>719</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.587285245039786</v>
       </c>
@@ -28404,7 +28239,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -28646,7 +28481,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -28798,9 +28633,6 @@
       <c r="O148" t="n">
         <v>43</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -28949,9 +28781,6 @@
       <c r="P149" t="n">
         <v>867</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.7081728893595194</v>
       </c>
@@ -29206,7 +29035,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -29448,7 +29277,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29600,9 +29429,6 @@
       <c r="O152" t="n">
         <v>29</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.008308610585031217</v>
       </c>
@@ -29751,9 +29577,6 @@
       <c r="P153" t="n">
         <v>669</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.5464448246614977</v>
       </c>
@@ -30008,7 +29831,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -30250,7 +30073,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -30402,9 +30225,6 @@
       <c r="O156" t="n">
         <v>32</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.009168122024862033</v>
       </c>
@@ -30553,9 +30373,6 @@
       <c r="P157" t="n">
         <v>648</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.5292918481026165</v>
       </c>
@@ -30810,7 +30627,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -31052,7 +30869,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31204,9 +31021,6 @@
       <c r="O160" t="n">
         <v>39</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1432396609612718</v>
       </c>
@@ -31595,16 +31409,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>568</v>
+        <v>669</v>
       </c>
       <c r="O162" t="n">
-        <v>568</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="R162" t="n">
-        <v>1.100766916713882</v>
+        <v>1.296501879016879</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -31748,9 +31559,6 @@
       <c r="O163" t="n">
         <v>37</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -31899,9 +31707,6 @@
       <c r="P164" t="n">
         <v>594</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.4851841940940652</v>
       </c>
@@ -32156,7 +31961,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32398,7 +32203,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -32475,6 +32280,151 @@
       <c r="BC166" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>41</v>
+      </c>
+      <c r="O167" t="n">
+        <v>41</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.01174665634435448</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32511,7 +32461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -32594,7 +32544,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -32604,7 +32554,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -32656,7 +32606,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>327972</v>
+        <v>328115</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -31409,13 +31409,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="O162" t="n">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="R162" t="n">
-        <v>1.296501879016879</v>
+        <v>1.323633457949967</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328115</v>
+        <v>328129</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -31016,13 +31016,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="O160" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1432396609612718</v>
+        <v>0.2644424510054249</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -31175,10 +31175,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="O161" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328129</v>
+        <v>328162</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -14276,10 +14276,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O73" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -14432,10 +14432,10 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O74" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -18459,10 +18459,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O95" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18615,10 +18615,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O96" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -23633,12 +23633,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23672,84 +23672,92 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>59438</v>
+        <v>63</v>
       </c>
       <c r="O122" t="n">
-        <v>59438</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>4.206766744261253</v>
+        <v>63</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23776,17 +23784,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -23820,81 +23828,170 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="O123" t="n">
-        <v>147</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1.992247311889163</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Chickenpox (Varicella)</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary chickenpox (varicella) notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23926,12 +24023,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -23965,13 +24062,16 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>3557</v>
+        <v>59438</v>
       </c>
       <c r="O124" t="n">
-        <v>3557</v>
+        <v>59438</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>6.893359018928308</v>
+        <v>4.206766744261253</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -24004,42 +24104,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24171,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24101,7 +24201,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24110,13 +24210,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="O125" t="n">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="R125" t="n">
-        <v>0.00974112965141591</v>
+        <v>1.992247311889163</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -24149,42 +24249,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24216,12 +24316,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -24246,7 +24346,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -24255,103 +24355,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>823</v>
+        <v>3557</v>
       </c>
       <c r="O126" t="n">
-        <v>823</v>
-      </c>
-      <c r="P126" t="n">
-        <v>823</v>
+        <v>3557</v>
       </c>
       <c r="R126" t="n">
-        <v>0.6722333194266257</v>
+        <v>6.893359018928308</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24378,17 +24456,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -24413,7 +24491,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -24422,178 +24500,81 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="O127" t="n">
-        <v>12</v>
-      </c>
-      <c r="P127" t="n">
-        <v>12</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
+        <v>34</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.00974112965141591</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
         <v>0</v>
       </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT127" t="n">
-        <v>2</v>
-      </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24620,7 +24601,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -24672,98 +24653,23 @@
       <c r="P128" t="n">
         <v>823</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.6722333194266257</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -24862,17 +24768,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -24897,7 +24803,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -24906,81 +24812,178 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="O129" t="n">
-        <v>42</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.01203316015763142</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="P129" t="n">
+        <v>12</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>0</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25010,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -25042,7 +25045,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -25051,31 +25054,106 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>987</v>
+        <v>823</v>
       </c>
       <c r="O130" t="n">
-        <v>987</v>
+        <v>823</v>
       </c>
       <c r="P130" t="n">
-        <v>987</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.8061898982674113</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>823</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -25174,17 +25252,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -25209,7 +25287,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -25218,178 +25296,81 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="O131" t="n">
-        <v>13</v>
-      </c>
-      <c r="P131" t="n">
-        <v>13</v>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
+        <v>42</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.01203316015763142</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
         <v>0</v>
       </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT131" t="n">
-        <v>2</v>
-      </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25416,7 +25397,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -25468,98 +25449,23 @@
       <c r="P132" t="n">
         <v>987</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.8061898982674113</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -25658,17 +25564,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -25693,7 +25599,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -25702,81 +25608,178 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O133" t="n">
-        <v>39</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.0111736487178006</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="P133" t="n">
+        <v>13</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>0</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25803,7 +25806,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -25838,7 +25841,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -25847,31 +25850,106 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>781</v>
+        <v>987</v>
       </c>
       <c r="O134" t="n">
-        <v>781</v>
+        <v>987</v>
       </c>
       <c r="P134" t="n">
-        <v>781</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0.6379273663088634</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>987</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -25970,17 +26048,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -26005,7 +26083,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -26014,178 +26092,81 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="O135" t="n">
-        <v>24</v>
-      </c>
-      <c r="P135" t="n">
-        <v>24</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
+        <v>39</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.0111736487178006</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
         <v>0</v>
       </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT135" t="n">
-        <v>2</v>
-      </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26212,7 +26193,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -26264,98 +26245,23 @@
       <c r="P136" t="n">
         <v>781</v>
       </c>
+      <c r="R136" t="n">
+        <v>0.6379273663088634</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -26454,17 +26360,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -26489,7 +26395,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -26498,81 +26404,178 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="O137" t="n">
-        <v>31</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.008881618211585096</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="P137" t="n">
+        <v>24</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>0</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26599,7 +26602,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -26634,7 +26637,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -26643,31 +26646,106 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>949</v>
+        <v>781</v>
       </c>
       <c r="O138" t="n">
-        <v>949</v>
+        <v>781</v>
       </c>
       <c r="P138" t="n">
-        <v>949</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0.7751511787799122</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>781</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -26766,17 +26844,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -26801,7 +26879,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -26810,178 +26888,81 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="O139" t="n">
-        <v>14</v>
-      </c>
-      <c r="P139" t="n">
-        <v>14</v>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
+        <v>31</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.008881618211585096</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
         <v>0</v>
       </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT139" t="n">
-        <v>2</v>
-      </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27008,7 +26989,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -27060,98 +27041,23 @@
       <c r="P140" t="n">
         <v>949</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.7751511787799122</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -27250,17 +27156,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -27285,104 +27191,187 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="O141" t="n">
-        <v>217</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.7970001648357945</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="P141" t="n">
+        <v>14</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>0</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27414,12 +27403,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -27444,53 +27433,56 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>217</v>
+        <v>949</v>
       </c>
       <c r="O142" t="n">
-        <v>217</v>
+        <v>949</v>
+      </c>
+      <c r="P142" t="n">
+        <v>949</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Varicella zoster (chickenpox)</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
@@ -27500,7 +27492,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -27540,12 +27532,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -27553,70 +27545,75 @@
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27648,12 +27645,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -27687,81 +27684,95 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2508</v>
+        <v>217</v>
       </c>
       <c r="O143" t="n">
-        <v>2508</v>
+        <v>217</v>
       </c>
       <c r="R143" t="n">
-        <v>4.860428568870451</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27788,17 +27799,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -27823,7 +27834,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -27832,81 +27843,170 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="O144" t="n">
-        <v>26</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.007449099145200401</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>217</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27938,12 +28038,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -27968,7 +28068,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -27977,103 +28077,81 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>719</v>
+        <v>2508</v>
       </c>
       <c r="O145" t="n">
-        <v>719</v>
-      </c>
-      <c r="P145" t="n">
-        <v>719</v>
+        <v>2508</v>
       </c>
       <c r="R145" t="n">
-        <v>0.587285245039786</v>
+        <v>4.860428568870451</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28100,17 +28178,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -28135,7 +28213,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -28144,178 +28222,81 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O146" t="n">
-        <v>15</v>
-      </c>
-      <c r="P146" t="n">
-        <v>15</v>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
+        <v>26</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.007449099145200401</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
         <v>0</v>
       </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT146" t="n">
-        <v>2</v>
-      </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28342,7 +28323,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -28394,98 +28375,23 @@
       <c r="P147" t="n">
         <v>719</v>
       </c>
+      <c r="R147" t="n">
+        <v>0.587285245039786</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -28584,17 +28490,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -28619,7 +28525,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -28628,81 +28534,178 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="O148" t="n">
-        <v>43</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="P148" t="n">
+        <v>15</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>0</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28729,7 +28732,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -28764,7 +28767,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -28773,31 +28776,106 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="O149" t="n">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="P149" t="n">
-        <v>867</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.7081728893595194</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>719</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -28896,17 +28974,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -28931,7 +29009,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -28940,178 +29018,81 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="O150" t="n">
-        <v>11</v>
-      </c>
-      <c r="P150" t="n">
-        <v>11</v>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
+        <v>43</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.01231966397090836</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
         <v>0</v>
       </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT150" t="n">
-        <v>2</v>
-      </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29119,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -29190,98 +29171,23 @@
       <c r="P151" t="n">
         <v>867</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.7081728893595194</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -29380,17 +29286,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29415,7 +29321,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -29424,81 +29330,178 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O152" t="n">
-        <v>29</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0.008308610585031217</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="P152" t="n">
+        <v>11</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>0</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29528,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -29560,7 +29563,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -29569,31 +29572,106 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>669</v>
+        <v>867</v>
       </c>
       <c r="O153" t="n">
-        <v>669</v>
+        <v>867</v>
       </c>
       <c r="P153" t="n">
-        <v>669</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0.5464448246614977</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>867</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -29692,17 +29770,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -29727,7 +29805,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -29736,178 +29814,81 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O154" t="n">
-        <v>13</v>
-      </c>
-      <c r="P154" t="n">
-        <v>13</v>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
+        <v>29</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.008308610585031217</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
         <v>0</v>
       </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT154" t="n">
-        <v>2</v>
-      </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29934,7 +29915,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -29986,98 +29967,23 @@
       <c r="P155" t="n">
         <v>669</v>
       </c>
+      <c r="R155" t="n">
+        <v>0.5464448246614977</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -30176,17 +30082,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -30211,7 +30117,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -30220,81 +30126,178 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O156" t="n">
-        <v>32</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.009168122024862033</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="P156" t="n">
+        <v>13</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>0</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30321,7 +30324,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -30356,7 +30359,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -30365,31 +30368,106 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="O157" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="P157" t="n">
-        <v>648</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.5292918481026165</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>669</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -30488,17 +30566,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -30523,7 +30601,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -30532,178 +30610,81 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="O158" t="n">
-        <v>12</v>
-      </c>
-      <c r="P158" t="n">
-        <v>12</v>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
+        <v>32</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.009168122024862033</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
         <v>0</v>
       </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT158" t="n">
-        <v>2</v>
-      </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30711,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -30782,98 +30763,23 @@
       <c r="P159" t="n">
         <v>648</v>
       </c>
+      <c r="R159" t="n">
+        <v>0.5292918481026165</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -30972,17 +30878,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -31007,104 +30913,187 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="O160" t="n">
-        <v>72</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0.2644424510054249</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="P160" t="n">
+        <v>12</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>0</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31136,12 +31125,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -31166,53 +31155,56 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>72</v>
+        <v>648</v>
       </c>
       <c r="O161" t="n">
-        <v>72</v>
+        <v>648</v>
+      </c>
+      <c r="P161" t="n">
+        <v>648</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Varicella zoster (chickenpox)</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
@@ -31222,7 +31214,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -31262,12 +31254,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -31275,70 +31267,75 @@
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31370,12 +31367,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -31409,81 +31406,95 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>683</v>
+        <v>93</v>
       </c>
       <c r="O162" t="n">
-        <v>683</v>
+        <v>93</v>
       </c>
       <c r="R162" t="n">
-        <v>1.323633457949967</v>
+        <v>0.3415714992153405</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31510,17 +31521,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -31554,81 +31565,170 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="O163" t="n">
-        <v>37</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.01060064109124673</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31660,12 +31760,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -31690,7 +31790,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -31699,103 +31799,81 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>594</v>
+        <v>683</v>
       </c>
       <c r="O164" t="n">
-        <v>594</v>
-      </c>
-      <c r="P164" t="n">
-        <v>594</v>
+        <v>683</v>
       </c>
       <c r="R164" t="n">
-        <v>0.4851841940940652</v>
+        <v>1.323633457949967</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31822,17 +31900,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -31857,7 +31935,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -31866,178 +31944,81 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="O165" t="n">
-        <v>19</v>
-      </c>
-      <c r="P165" t="n">
-        <v>19</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
+        <v>37</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.01060064109124673</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
         <v>0</v>
       </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT165" t="n">
-        <v>2</v>
-      </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32064,7 +32045,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -32116,98 +32097,23 @@
       <c r="P166" t="n">
         <v>594</v>
       </c>
+      <c r="R166" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -32306,123 +32212,607 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>19</v>
+      </c>
+      <c r="O167" t="n">
+        <v>19</v>
+      </c>
+      <c r="P167" t="n">
+        <v>19</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>594</v>
+      </c>
+      <c r="O168" t="n">
+        <v>594</v>
+      </c>
+      <c r="P168" t="n">
+        <v>594</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N167" t="n">
+      <c r="N169" t="n">
         <v>41</v>
       </c>
-      <c r="O167" t="n">
+      <c r="O169" t="n">
         <v>41</v>
       </c>
-      <c r="R167" t="n">
+      <c r="R169" t="n">
         <v>0.01174665634435448</v>
       </c>
-      <c r="S167" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO167" t="inlineStr">
+      <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP167" t="inlineStr">
+      <c r="AP169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR167" t="inlineStr">
+      <c r="AR169" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS167" t="inlineStr"/>
-      <c r="AT167" t="n">
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
         <v>0</v>
       </c>
-      <c r="AU167" t="inlineStr">
+      <c r="AU169" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV167" t="inlineStr">
+      <c r="AV169" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW167" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX167" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ167" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA167" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB167" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC167" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -32544,7 +32934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -32554,7 +32944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -32574,7 +32964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -32606,7 +32996,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328162</v>
+        <v>328248</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -27684,13 +27684,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O143" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R143" t="n">
-        <v>0.7970001648357945</v>
+        <v>0.8006729766553142</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27843,10 +27843,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O144" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -28077,13 +28077,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="O145" t="n">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="R145" t="n">
-        <v>4.860428568870451</v>
+        <v>4.862366538794243</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -31406,13 +31406,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O162" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="R162" t="n">
-        <v>0.3415714992153405</v>
+        <v>0.3746268055910186</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -31565,10 +31565,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O163" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -31799,13 +31799,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>683</v>
+        <v>828</v>
       </c>
       <c r="O164" t="n">
-        <v>683</v>
+        <v>828</v>
       </c>
       <c r="R164" t="n">
-        <v>1.323633457949967</v>
+        <v>1.604639096899814</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -32815,6 +32815,657 @@
       <c r="BC169" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>555</v>
+      </c>
+      <c r="O170" t="n">
+        <v>555</v>
+      </c>
+      <c r="P170" t="n">
+        <v>555</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>11</v>
+      </c>
+      <c r="O171" t="n">
+        <v>11</v>
+      </c>
+      <c r="P171" t="n">
+        <v>11</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>555</v>
+      </c>
+      <c r="O172" t="n">
+        <v>555</v>
+      </c>
+      <c r="P172" t="n">
+        <v>555</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32851,7 +33502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -32934,7 +33585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -32944,7 +33595,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -32964,7 +33615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -32996,7 +33647,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328248</v>
+        <v>328959</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -28038,12 +28038,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -28077,13 +28077,16 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>2509</v>
+        <v>46105</v>
       </c>
       <c r="O145" t="n">
-        <v>2509</v>
+        <v>46105</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>4.862366538794243</v>
+        <v>3.263114181906609</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -28116,42 +28119,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -28183,12 +28186,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -28213,7 +28216,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -28222,13 +28225,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>26</v>
+        <v>2509</v>
       </c>
       <c r="O146" t="n">
-        <v>26</v>
+        <v>2509</v>
       </c>
       <c r="R146" t="n">
-        <v>0.007449099145200401</v>
+        <v>4.862366538794243</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -28261,42 +28264,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28328,12 +28331,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -28358,7 +28361,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -28367,103 +28370,81 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>719</v>
+        <v>26</v>
       </c>
       <c r="O147" t="n">
-        <v>719</v>
-      </c>
-      <c r="P147" t="n">
-        <v>719</v>
+        <v>26</v>
       </c>
       <c r="R147" t="n">
-        <v>0.587285245039786</v>
+        <v>0.007449099145200401</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28471,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -28534,106 +28515,31 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>15</v>
+        <v>719</v>
       </c>
       <c r="O148" t="n">
-        <v>15</v>
+        <v>719</v>
       </c>
       <c r="P148" t="n">
-        <v>15</v>
+        <v>719</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.587285245039786</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>0</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -28776,22 +28682,22 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="O149" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="P149" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -28801,17 +28707,17 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -28866,7 +28772,7 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
@@ -28875,7 +28781,7 @@
         </is>
       </c>
       <c r="AN149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -28974,17 +28880,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29009,7 +28915,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -29018,81 +28924,178 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>43</v>
+        <v>719</v>
       </c>
       <c r="O150" t="n">
-        <v>43</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>719</v>
+      </c>
+      <c r="P150" t="n">
+        <v>719</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29124,12 +29127,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29154,7 +29157,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -29163,103 +29166,81 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>867</v>
+        <v>43</v>
       </c>
       <c r="O151" t="n">
-        <v>867</v>
-      </c>
-      <c r="P151" t="n">
-        <v>867</v>
+        <v>43</v>
       </c>
       <c r="R151" t="n">
-        <v>0.7081728893595194</v>
+        <v>0.01231966397090836</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29286,7 +29267,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -29330,106 +29311,31 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>11</v>
+        <v>867</v>
       </c>
       <c r="O152" t="n">
-        <v>11</v>
+        <v>867</v>
       </c>
       <c r="P152" t="n">
-        <v>11</v>
+        <v>867</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.7081728893595194</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>0</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -29572,22 +29478,22 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="O153" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="P153" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
@@ -29597,17 +29503,17 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -29662,7 +29568,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -29671,7 +29577,7 @@
         </is>
       </c>
       <c r="AN153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -29770,17 +29676,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -29805,7 +29711,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -29814,81 +29720,178 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>29</v>
+        <v>867</v>
       </c>
       <c r="O154" t="n">
-        <v>29</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.008308610585031217</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>867</v>
+      </c>
+      <c r="P154" t="n">
+        <v>867</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29920,12 +29923,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -29950,7 +29953,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -29959,103 +29962,81 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>669</v>
+        <v>29</v>
       </c>
       <c r="O155" t="n">
-        <v>669</v>
-      </c>
-      <c r="P155" t="n">
-        <v>669</v>
+        <v>29</v>
       </c>
       <c r="R155" t="n">
-        <v>0.5464448246614977</v>
+        <v>0.008308610585031217</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30082,7 +30063,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -30126,106 +30107,31 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>13</v>
+        <v>669</v>
       </c>
       <c r="O156" t="n">
-        <v>13</v>
+        <v>669</v>
       </c>
       <c r="P156" t="n">
-        <v>13</v>
+        <v>669</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.5464448246614977</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>0</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -30368,22 +30274,22 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="O157" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="P157" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -30393,17 +30299,17 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -30458,7 +30364,7 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -30467,7 +30373,7 @@
         </is>
       </c>
       <c r="AN157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -30566,17 +30472,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -30601,7 +30507,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -30610,81 +30516,178 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>32</v>
+        <v>669</v>
       </c>
       <c r="O158" t="n">
-        <v>32</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0.009168122024862033</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>669</v>
+      </c>
+      <c r="P158" t="n">
+        <v>669</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30716,12 +30719,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -30746,7 +30749,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -30755,103 +30758,81 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>648</v>
+        <v>32</v>
       </c>
       <c r="O159" t="n">
-        <v>648</v>
-      </c>
-      <c r="P159" t="n">
-        <v>648</v>
+        <v>32</v>
       </c>
       <c r="R159" t="n">
-        <v>0.5292918481026165</v>
+        <v>0.009168122024862033</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30859,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -30922,106 +30903,31 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>12</v>
+        <v>648</v>
       </c>
       <c r="O160" t="n">
-        <v>12</v>
+        <v>648</v>
       </c>
       <c r="P160" t="n">
-        <v>12</v>
+        <v>648</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.5292918481026165</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>0</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
@@ -31164,22 +31070,22 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="O161" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="P161" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -31189,17 +31095,17 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -31254,7 +31160,7 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -31263,7 +31169,7 @@
         </is>
       </c>
       <c r="AN161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -31362,17 +31268,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -31397,104 +31303,187 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>102</v>
+        <v>648</v>
       </c>
       <c r="O162" t="n">
-        <v>102</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.3746268055910186</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>648</v>
+      </c>
+      <c r="P162" t="n">
+        <v>648</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31510,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -31570,98 +31559,23 @@
       <c r="O163" t="n">
         <v>102</v>
       </c>
+      <c r="R163" t="n">
+        <v>0.3746268055910186</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>SER_AU_VARICELLA_CHICKENPOX</t>
         </is>
       </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Varicella zoster (chickenpox)</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
@@ -31755,17 +31669,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -31799,81 +31713,170 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>828</v>
+        <v>102</v>
       </c>
       <c r="O164" t="n">
-        <v>828</v>
-      </c>
-      <c r="R164" t="n">
-        <v>1.604639096899814</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>102</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31905,12 +31908,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -31944,13 +31947,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>37</v>
+        <v>828</v>
       </c>
       <c r="O165" t="n">
-        <v>37</v>
+        <v>828</v>
       </c>
       <c r="R165" t="n">
-        <v>0.01060064109124673</v>
+        <v>1.604639096899814</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -31983,42 +31986,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32050,12 +32053,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -32080,7 +32083,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -32089,103 +32092,81 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="O166" t="n">
-        <v>594</v>
-      </c>
-      <c r="P166" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="R166" t="n">
-        <v>0.4851841940940652</v>
+        <v>0.01060064109124673</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32212,7 +32193,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -32256,106 +32237,31 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="O167" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="P167" t="n">
-        <v>19</v>
+        <v>594</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE167" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF167" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN167" t="b">
-        <v>0</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
@@ -32498,22 +32404,22 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="O168" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="P168" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
@@ -32523,17 +32429,17 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -32588,7 +32494,7 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
@@ -32597,7 +32503,7 @@
         </is>
       </c>
       <c r="AN168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -32696,17 +32602,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -32731,7 +32637,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -32740,81 +32646,178 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>41</v>
+        <v>594</v>
       </c>
       <c r="O169" t="n">
-        <v>41</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>594</v>
+      </c>
+      <c r="P169" t="n">
+        <v>594</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32846,12 +32849,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -32876,7 +32879,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -32885,103 +32888,81 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="O170" t="n">
-        <v>555</v>
-      </c>
-      <c r="P170" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="R170" t="n">
-        <v>0.4533286661990003</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33008,7 +32989,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -33052,106 +33033,31 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="O171" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="P171" t="n">
-        <v>11</v>
+        <v>555</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>0</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -33294,22 +33200,22 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="O172" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="P172" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -33319,17 +33225,17 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -33384,7 +33290,7 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -33393,7 +33299,7 @@
         </is>
       </c>
       <c r="AN172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -33464,6 +33370,248 @@
         </is>
       </c>
       <c r="BC172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>555</v>
+      </c>
+      <c r="O173" t="n">
+        <v>555</v>
+      </c>
+      <c r="P173" t="n">
+        <v>555</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -33585,7 +33733,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -33595,7 +33743,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -33647,7 +33795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328959</v>
+        <v>375064</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -23279,13 +23279,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O120" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R120" t="n">
-        <v>0.5729586438450872</v>
+        <v>0.5766314556646071</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23438,10 +23438,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O121" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -27684,13 +27684,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O143" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R143" t="n">
-        <v>0.8006729766553142</v>
+        <v>0.8043457884748341</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27843,10 +27843,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O144" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -33614,6 +33614,151 @@
       <c r="BC173" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>38</v>
+      </c>
+      <c r="O174" t="n">
+        <v>38</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33650,7 +33795,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -33733,7 +33878,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -33743,7 +33888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -33795,7 +33940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375064</v>
+        <v>375104</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -24355,13 +24355,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>3557</v>
+        <v>3561</v>
       </c>
       <c r="O126" t="n">
-        <v>3557</v>
+        <v>3561</v>
       </c>
       <c r="R126" t="n">
-        <v>6.893359018928308</v>
+        <v>6.901110898623476</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -28225,13 +28225,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="O146" t="n">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="R146" t="n">
-        <v>4.862366538794243</v>
+        <v>4.86818044856562</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -31947,13 +31947,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>828</v>
+        <v>1308</v>
       </c>
       <c r="O165" t="n">
-        <v>828</v>
+        <v>1308</v>
       </c>
       <c r="R165" t="n">
-        <v>1.604639096899814</v>
+        <v>2.534864660319996</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -33759,6 +33759,657 @@
       <c r="BC174" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>386</v>
+      </c>
+      <c r="O175" t="n">
+        <v>386</v>
+      </c>
+      <c r="P175" t="n">
+        <v>386</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.3152880453203858</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>12</v>
+      </c>
+      <c r="O176" t="n">
+        <v>12</v>
+      </c>
+      <c r="P176" t="n">
+        <v>12</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>386</v>
+      </c>
+      <c r="O177" t="n">
+        <v>386</v>
+      </c>
+      <c r="P177" t="n">
+        <v>386</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33795,7 +34446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -33878,7 +34529,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -33888,7 +34539,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -33908,7 +34559,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -33940,7 +34591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375104</v>
+        <v>375977</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -31947,13 +31947,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="O165" t="n">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="R165" t="n">
-        <v>2.534864660319996</v>
+        <v>2.552306389634124</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375977</v>
+        <v>375986</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -30601,7 +30601,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34323,7 +34323,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34410,6 +34410,151 @@
       <c r="BC177" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>43</v>
+      </c>
+      <c r="O178" t="n">
+        <v>43</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.01231966397090836</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34446,7 +34591,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -34529,7 +34674,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -34539,7 +34684,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -34591,7 +34736,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375986</v>
+        <v>376029</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -30601,7 +30601,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34323,7 +34323,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -30601,7 +30601,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34323,7 +34323,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -28186,12 +28186,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -28225,13 +28225,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>2512</v>
+        <v>136</v>
       </c>
       <c r="O146" t="n">
-        <v>2512</v>
+        <v>136</v>
       </c>
       <c r="R146" t="n">
-        <v>4.86818044856562</v>
+        <v>1.843167581067525</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -28264,42 +28264,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28331,12 +28331,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -28370,13 +28370,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>26</v>
+        <v>2516</v>
       </c>
       <c r="O147" t="n">
-        <v>26</v>
+        <v>2516</v>
       </c>
       <c r="R147" t="n">
-        <v>0.007449099145200401</v>
+        <v>4.875932328260788</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -28409,42 +28409,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -28515,103 +28515,81 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>719</v>
+        <v>26</v>
       </c>
       <c r="O148" t="n">
-        <v>719</v>
-      </c>
-      <c r="P148" t="n">
-        <v>719</v>
+        <v>26</v>
       </c>
       <c r="R148" t="n">
-        <v>0.587285245039786</v>
+        <v>0.007449099145200401</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28638,7 +28616,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -28682,106 +28660,31 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>15</v>
+        <v>719</v>
       </c>
       <c r="O149" t="n">
-        <v>15</v>
+        <v>719</v>
       </c>
       <c r="P149" t="n">
-        <v>15</v>
+        <v>719</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.587285245039786</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>0</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -28924,22 +28827,22 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="O150" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="P150" t="n">
-        <v>719</v>
+        <v>15</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -28949,17 +28852,17 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -29014,7 +28917,7 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -29023,7 +28926,7 @@
         </is>
       </c>
       <c r="AN150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -29122,17 +29025,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29157,7 +29060,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -29166,81 +29069,178 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>43</v>
+        <v>719</v>
       </c>
       <c r="O151" t="n">
-        <v>43</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>719</v>
+      </c>
+      <c r="P151" t="n">
+        <v>719</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29272,12 +29272,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -29311,103 +29311,81 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>867</v>
+        <v>43</v>
       </c>
       <c r="O152" t="n">
-        <v>867</v>
-      </c>
-      <c r="P152" t="n">
-        <v>867</v>
+        <v>43</v>
       </c>
       <c r="R152" t="n">
-        <v>0.7081728893595194</v>
+        <v>0.01231966397090836</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29412,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -29478,106 +29456,31 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>11</v>
+        <v>867</v>
       </c>
       <c r="O153" t="n">
-        <v>11</v>
+        <v>867</v>
       </c>
       <c r="P153" t="n">
-        <v>11</v>
+        <v>867</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.7081728893595194</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>0</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -29720,22 +29623,22 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="O154" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="P154" t="n">
-        <v>867</v>
+        <v>11</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -29745,17 +29648,17 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -29810,7 +29713,7 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -29819,7 +29722,7 @@
         </is>
       </c>
       <c r="AN154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -29918,17 +29821,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -29953,7 +29856,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -29962,81 +29865,178 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>29</v>
+        <v>867</v>
       </c>
       <c r="O155" t="n">
-        <v>29</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.008308610585031217</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>867</v>
+      </c>
+      <c r="P155" t="n">
+        <v>867</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30068,12 +30068,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -30107,103 +30107,81 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>669</v>
+        <v>29</v>
       </c>
       <c r="O156" t="n">
-        <v>669</v>
-      </c>
-      <c r="P156" t="n">
-        <v>669</v>
+        <v>29</v>
       </c>
       <c r="R156" t="n">
-        <v>0.5464448246614977</v>
+        <v>0.008308610585031217</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30230,7 +30208,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -30274,106 +30252,31 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>13</v>
+        <v>669</v>
       </c>
       <c r="O157" t="n">
-        <v>13</v>
+        <v>669</v>
       </c>
       <c r="P157" t="n">
-        <v>13</v>
+        <v>669</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.5464448246614977</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>0</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -30516,22 +30419,22 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="O158" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="P158" t="n">
-        <v>669</v>
+        <v>13</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
@@ -30541,17 +30444,17 @@
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -30606,7 +30509,7 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
@@ -30615,7 +30518,7 @@
         </is>
       </c>
       <c r="AN158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -30714,17 +30617,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -30749,7 +30652,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -30758,81 +30661,178 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>32</v>
+        <v>669</v>
       </c>
       <c r="O159" t="n">
-        <v>32</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.009168122024862033</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>669</v>
+      </c>
+      <c r="P159" t="n">
+        <v>669</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30864,12 +30864,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -30903,103 +30903,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>648</v>
+        <v>32</v>
       </c>
       <c r="O160" t="n">
-        <v>648</v>
-      </c>
-      <c r="P160" t="n">
-        <v>648</v>
+        <v>32</v>
       </c>
       <c r="R160" t="n">
-        <v>0.5292918481026165</v>
+        <v>0.009168122024862033</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31026,7 +31004,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -31070,106 +31048,31 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>12</v>
+        <v>648</v>
       </c>
       <c r="O161" t="n">
-        <v>12</v>
+        <v>648</v>
       </c>
       <c r="P161" t="n">
-        <v>12</v>
+        <v>648</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.5292918481026165</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>0</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -31312,22 +31215,22 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="O162" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="P162" t="n">
-        <v>648</v>
+        <v>12</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
@@ -31337,17 +31240,17 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -31402,7 +31305,7 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -31411,7 +31314,7 @@
         </is>
       </c>
       <c r="AN162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -31510,17 +31413,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -31545,104 +31448,187 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>102</v>
+        <v>648</v>
       </c>
       <c r="O163" t="n">
-        <v>102</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.3746268055910186</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>648</v>
+      </c>
+      <c r="P163" t="n">
+        <v>648</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31669,7 +31655,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -31718,98 +31704,23 @@
       <c r="O164" t="n">
         <v>102</v>
       </c>
+      <c r="R164" t="n">
+        <v>0.3746268055910186</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>SER_AU_VARICELLA_CHICKENPOX</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Varicella zoster (chickenpox)</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -31903,17 +31814,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -31947,81 +31858,170 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1317</v>
+        <v>102</v>
       </c>
       <c r="O165" t="n">
-        <v>1317</v>
-      </c>
-      <c r="R165" t="n">
-        <v>2.552306389634124</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>102</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32053,12 +32053,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -32092,13 +32092,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>37</v>
+        <v>1353</v>
       </c>
       <c r="O166" t="n">
-        <v>37</v>
+        <v>1353</v>
       </c>
       <c r="R166" t="n">
-        <v>0.01060064109124673</v>
+        <v>2.622073306890638</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -32131,42 +32131,42 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32198,12 +32198,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -32228,7 +32228,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -32237,103 +32237,81 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="O167" t="n">
-        <v>594</v>
-      </c>
-      <c r="P167" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="R167" t="n">
-        <v>0.4851841940940652</v>
+        <v>0.01060064109124673</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32360,7 +32338,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -32404,106 +32382,31 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="O168" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="P168" t="n">
-        <v>19</v>
+        <v>594</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>0</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -32646,22 +32549,22 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="O169" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="P169" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
@@ -32671,17 +32574,17 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -32736,7 +32639,7 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
@@ -32745,7 +32648,7 @@
         </is>
       </c>
       <c r="AN169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -32844,17 +32747,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -32879,7 +32782,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -32888,81 +32791,178 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>41</v>
+        <v>594</v>
       </c>
       <c r="O170" t="n">
-        <v>41</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>594</v>
+      </c>
+      <c r="P170" t="n">
+        <v>594</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32994,12 +32994,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -33024,7 +33024,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -33033,103 +33033,81 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="O171" t="n">
-        <v>555</v>
-      </c>
-      <c r="P171" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="R171" t="n">
-        <v>0.4533286661990003</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33156,7 +33134,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -33200,106 +33178,31 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="O172" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="P172" t="n">
-        <v>11</v>
+        <v>555</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>0</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -33442,22 +33345,22 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="O173" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="P173" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -33467,17 +33370,17 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -33532,7 +33435,7 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -33541,7 +33444,7 @@
         </is>
       </c>
       <c r="AN173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
@@ -33640,17 +33543,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -33675,7 +33578,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -33684,81 +33587,178 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>38</v>
+        <v>555</v>
       </c>
       <c r="O174" t="n">
-        <v>38</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>555</v>
+      </c>
+      <c r="P174" t="n">
+        <v>555</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN174" t="b">
+        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33790,12 +33790,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -33820,7 +33820,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -33829,103 +33829,81 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="O175" t="n">
-        <v>386</v>
-      </c>
-      <c r="P175" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="R175" t="n">
-        <v>0.3152880453203858</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33952,7 +33930,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -33996,106 +33974,31 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="O176" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="P176" t="n">
-        <v>12</v>
+        <v>386</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0.3152880453203858</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>0</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -34238,22 +34141,22 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="O177" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="P177" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
@@ -34263,17 +34166,17 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -34328,7 +34231,7 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -34337,7 +34240,7 @@
         </is>
       </c>
       <c r="AN177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
@@ -34436,123 +34339,365 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>386</v>
+      </c>
+      <c r="O178" t="n">
+        <v>386</v>
+      </c>
+      <c r="P178" t="n">
+        <v>386</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN178" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N178" t="n">
+      <c r="N179" t="n">
         <v>43</v>
       </c>
-      <c r="O178" t="n">
+      <c r="O179" t="n">
         <v>43</v>
       </c>
-      <c r="R178" t="n">
+      <c r="R179" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S178" t="inlineStr">
+      <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO178" t="inlineStr">
+      <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP178" t="inlineStr">
+      <c r="AP179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR178" t="inlineStr">
+      <c r="AR179" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr"/>
-      <c r="AT178" t="n">
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="n">
         <v>0</v>
       </c>
-      <c r="AU178" t="inlineStr">
+      <c r="AU179" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV178" t="inlineStr">
+      <c r="AV179" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW178" t="inlineStr">
+      <c r="AW179" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX178" t="inlineStr">
+      <c r="AX179" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY178" t="inlineStr">
+      <c r="AY179" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ178" t="inlineStr">
+      <c r="AZ179" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA178" t="inlineStr">
+      <c r="BA179" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB178" t="inlineStr">
+      <c r="BB179" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC178" t="inlineStr">
+      <c r="BC179" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34674,7 +34819,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -34684,7 +34829,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -34736,7 +34881,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>376029</v>
+        <v>376205</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28912,7 +28912,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29950,7 +29950,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31300,7 +31300,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32876,7 +32876,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33430,7 +33430,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34468,7 +34468,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -35216,13 +35216,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="O188" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="R188" t="n">
-        <v>3.259665411818221</v>
+        <v>3.261603381742013</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -38690,13 +38690,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R206" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -38849,10 +38849,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
@@ -39083,13 +39083,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O208" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R208" t="n">
-        <v>0.1550375939033637</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>377802</v>
+        <v>377807</v>
       </c>
     </row>
     <row r="16">
